--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/OKLAHOMA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/OKLAHOMA_2018.xlsx
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C159">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C248">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C549">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C551">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C610">
